--- a/Docs/像素冒险：裂缝之刃_玩家技能设计.xlsx
+++ b/Docs/像素冒险：裂缝之刃_玩家技能设计.xlsx
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -477,7 +477,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>自动释放条件</t>
+          <t>释放时机建议</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -507,12 +507,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>生命低于 50% 时自动释放，瞬间恢复 30% 最大生命。冷却 12 秒，即时生效。</t>
+          <t>瞬间恢复 30% 最大生命。冷却 12 秒，即时生效。</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>生命低于 50% 且周围有敌人时释放</t>
+          <t>血量危险时手动点击</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>生命低于 60% 或被包围时自动释放，获得 35% 最大生命的护盾，持续 5 秒，期间免疫控制。冷却 18 秒。</t>
+          <t>获得 35% 最大生命的护盾，持续 5 秒，期间免疫控制。冷却 18 秒。</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>生命低于 60% 且进入精英/Boss 战或同时被 3 个以上敌人攻击时释放</t>
+          <t>精英/Boss 放大招前、或被包围时手动点击</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>通过第一章或 Lv3</t>
+          <t>通关第一章，在石碑上领悟防御架势</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>进入战斗后自动释放，攻击提升 +30%，持续 8 秒。冷却 18 秒。</t>
+          <t>攻击提升 +30%，持续 8 秒。冷却 18 秒。</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>进入战斗后冷却完毕即释放，优先在精英/Boss 战中</t>
+          <t>精英/Boss 战或大量小怪时手动点击</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>通过第二章或 Lv5</t>
+          <t>通关第二章，拾取格雷的战技笔记</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>进入战斗后自动释放，攻速提升 +35%，持续 6 秒。冷却 15 秒。</t>
+          <t>攻速提升 +35%，持续 6 秒。冷却 15 秒。</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>进入战斗后冷却完毕即释放</t>
+          <t>输出窗口期手动点击</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>通过第三章或 Lv8</t>
+          <t>通关第三章，解读神庙盾牌碎片上的步法</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>遇到精英/Boss 时自动释放，暴击率提升 +25%，持续 8 秒。冷却 18 秒。</t>
+          <t>暴击率提升 +25%，持续 8 秒。冷却 18 秒。</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>冷却完毕且周围有精英/Boss 时释放</t>
+          <t>Boss 战或精英怪出现时手动点击</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>通过第四章或 Lv12</t>
+          <t>通关第四章，取回灯塔上的猎人笔记</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>怪群或 Boss 虚弱时自动释放，造成 300% 攻击的范围伤害。冷却 25 秒，即时生效。</t>
+          <t>造成 300% 攻击的范围伤害。冷却 25 秒，即时生效。</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>同时存在 4 个以上敌人，或 Boss 进入虚弱/召唤小怪阶段时释放</t>
+          <t>怪群聚集或 Boss 虚弱时手动点击</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>通过第五章或 Lv15</t>
+          <t>通关第五章，吸收风车崩溃时的裂缝雷电</t>
         </is>
       </c>
     </row>
